--- a/tabla_estadistica_tamano_SNEDDS.xlsx
+++ b/tabla_estadistica_tamano_SNEDDS.xlsx
@@ -506,13 +506,13 @@
         <v>25.94</v>
       </c>
       <c r="C4" t="n">
-        <v>0.41</v>
+        <v>0.72</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.73</v>
+        <v>26.19</v>
       </c>
       <c r="C5" t="n">
-        <v>5.43</v>
+        <v>0.38</v>
       </c>
       <c r="D5" t="n">
         <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9</v>
+        <v>1.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No válido</t>
+          <t>Válido</t>
         </is>
       </c>
     </row>
